--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
   <si>
     <t>s/n</t>
   </si>
@@ -112,9 +112,6 @@
     <t>Delivery Invoice</t>
   </si>
   <si>
-    <t>Searchng, List and detaisl</t>
-  </si>
-  <si>
     <t>Delivery</t>
   </si>
   <si>
@@ -185,6 +182,15 @@
   </si>
   <si>
     <t>in edit shiping address</t>
+  </si>
+  <si>
+    <t>Searchng, List and details</t>
+  </si>
+  <si>
+    <t>working on Print</t>
+  </si>
+  <si>
+    <t>Edit Details  Requried</t>
   </si>
 </sst>
 </file>
@@ -268,24 +274,26 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -599,13 +607,13 @@
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
@@ -619,7 +627,7 @@
       <c r="C4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -641,7 +649,7 @@
       <c r="C5" s="2">
         <v>10</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="E5" s="4" t="s">
@@ -659,7 +667,7 @@
       <c r="C6" s="2">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E6" s="4" t="s">
@@ -674,19 +682,19 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
-      <c r="C7" s="5">
+      <c r="C7" s="3">
         <v>11</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H7" s="2"/>
@@ -694,19 +702,19 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="2"/>
-      <c r="C8" s="5">
+      <c r="C8" s="3">
         <v>12</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G8" s="5" t="s">
+      <c r="F8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="2"/>
@@ -717,7 +725,7 @@
       <c r="C9" s="2">
         <v>13</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
@@ -726,7 +734,7 @@
       <c r="F9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="5">
         <v>0.2</v>
       </c>
       <c r="H9" s="2" t="s">
@@ -739,7 +747,7 @@
       <c r="C10" s="2">
         <v>13</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="E10" s="2" t="s">
@@ -754,19 +762,19 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="2"/>
-      <c r="C11" s="5">
+      <c r="C11" s="3">
         <v>14</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="H11" s="2"/>
@@ -774,19 +782,21 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
-      <c r="C12" s="5">
+      <c r="C12" s="3">
         <v>15</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="5"/>
+      <c r="E12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>14</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
     </row>
@@ -795,7 +805,7 @@
       <c r="C13" s="2">
         <v>16</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="E13" s="2" t="s">
@@ -805,28 +815,28 @@
         <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="2"/>
-      <c r="C14" s="8">
+      <c r="C14" s="6">
         <v>17</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E14" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8" t="s">
-        <v>45</v>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
+        <v>44</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -835,11 +845,11 @@
       <c r="C15" s="2">
         <v>17</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
@@ -853,17 +863,17 @@
       <c r="C16" s="2">
         <v>18</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>34</v>
-      </c>
       <c r="F16" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="G16" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>56</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -873,17 +883,21 @@
       <c r="C17" s="2">
         <v>18</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+        <v>11</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
@@ -891,11 +905,11 @@
       <c r="C18" s="2">
         <v>19</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="D18" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>8</v>
@@ -909,11 +923,11 @@
       <c r="C19" s="2">
         <v>20</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
@@ -927,16 +941,16 @@
       <c r="C20" s="2">
         <v>21</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I20" s="2"/>
     </row>
@@ -945,11 +959,11 @@
       <c r="C21" s="2">
         <v>22</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>8</v>
@@ -963,11 +977,11 @@
       <c r="C22" s="2">
         <v>23</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>8</v>
@@ -978,38 +992,38 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
-      <c r="C23" s="5">
+      <c r="C23" s="3">
         <v>23</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E23" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="F23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
       <c r="I23" s="2"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B24" s="2"/>
-      <c r="C24" s="5">
+      <c r="C24" s="3">
         <v>24</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="5" t="s">
+      <c r="D24" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="F24" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="E24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
       <c r="I24" s="2"/>
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.25">
@@ -1017,11 +1031,11 @@
       <c r="C25" s="2">
         <v>24</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>51</v>
+      <c r="D25" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>8</v>
@@ -1033,7 +1047,7 @@
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="D26" s="3"/>
+      <c r="D26" s="2"/>
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
@@ -1043,7 +1057,7 @@
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="D27" s="3"/>
+      <c r="D27" s="2"/>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>s/n</t>
   </si>
@@ -106,9 +106,6 @@
     <t>Dispactch list , delivery, Edit</t>
   </si>
   <si>
-    <t>excel dispath list,  copy, coplete</t>
-  </si>
-  <si>
     <t>Delivery Invoice</t>
   </si>
   <si>
@@ -121,15 +118,9 @@
     <t>cancel</t>
   </si>
   <si>
-    <t>Print edit</t>
-  </si>
-  <si>
     <t>All status</t>
   </si>
   <si>
-    <t>Pint Edit</t>
-  </si>
-  <si>
     <t>Send percel</t>
   </si>
   <si>
@@ -187,10 +178,19 @@
     <t>Searchng, List and details</t>
   </si>
   <si>
-    <t>working on Print</t>
-  </si>
-  <si>
     <t>Edit Details  Requried</t>
+  </si>
+  <si>
+    <t>List, Print  edit</t>
+  </si>
+  <si>
+    <t>List, Print Edit</t>
+  </si>
+  <si>
+    <t>Edit Detail Info Requred</t>
+  </si>
+  <si>
+    <t>excel dispath list,  copy, complete</t>
   </si>
 </sst>
 </file>
@@ -607,7 +607,7 @@
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:9" x14ac:dyDescent="0.25">
@@ -789,7 +789,7 @@
         <v>27</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>8</v>
@@ -815,7 +815,7 @@
         <v>8</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -826,17 +826,17 @@
         <v>17</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G14" s="6"/>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -846,10 +846,10 @@
         <v>17</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>8</v>
@@ -864,58 +864,62 @@
         <v>18</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="F16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B17" s="2"/>
-      <c r="C17" s="2">
+      <c r="C17" s="3">
         <v>18</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>57</v>
+      <c r="G17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="I17" s="2"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B18" s="2"/>
-      <c r="C18" s="2">
+      <c r="C18" s="3">
         <v>19</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="D18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
@@ -924,10 +928,10 @@
         <v>20</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>8</v>
@@ -942,15 +946,15 @@
         <v>21</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
       <c r="H20" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="I20" s="2"/>
     </row>
@@ -960,10 +964,10 @@
         <v>22</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>8</v>
@@ -978,10 +982,10 @@
         <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>8</v>
@@ -996,10 +1000,10 @@
         <v>23</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>8</v>
@@ -1014,10 +1018,10 @@
         <v>24</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>8</v>
@@ -1032,10 +1036,10 @@
         <v>24</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>8</v>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
   <si>
     <t>s/n</t>
   </si>
@@ -191,13 +191,16 @@
   </si>
   <si>
     <t>excel dispath list,  copy, complete</t>
+  </si>
+  <si>
+    <t>details required (Copy pending)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -214,20 +217,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,11 +233,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -269,12 +260,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -285,19 +275,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
-    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -356,7 +342,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -391,7 +377,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -821,22 +807,22 @@
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B14" s="2"/>
-      <c r="C14" s="6">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3">
         <v>17</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6" t="s">
-        <v>41</v>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3" t="s">
+        <v>59</v>
       </c>
       <c r="I14" s="2"/>
     </row>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>s/n</t>
   </si>
@@ -909,21 +909,21 @@
       <c r="I18" s="2"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3">
         <v>20</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="F19" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
       <c r="I19" s="2"/>
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
@@ -977,7 +977,9 @@
         <v>8</v>
       </c>
       <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
+      <c r="H22" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="I22" s="2"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -828,20 +828,20 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
-      <c r="C15" s="2">
+      <c r="C15" s="3">
         <v>17</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
       <c r="I15" s="2"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -342,7 +342,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -377,7 +377,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
   <si>
     <t>s/n</t>
   </si>
@@ -161,9 +161,6 @@
   </si>
   <si>
     <t>Process order list, print, Edit and cancel</t>
-  </si>
-  <si>
-    <t>working on Edit</t>
   </si>
   <si>
     <t>excel dispath</t>
@@ -788,22 +785,22 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B13" s="2"/>
-      <c r="C13" s="2">
+      <c r="C13" s="3">
         <v>16</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="2"/>
+      <c r="F13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="3"/>
       <c r="I13" s="2"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
@@ -812,17 +809,17 @@
         <v>17</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>50</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>51</v>
       </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I14" s="2"/>
     </row>
@@ -835,7 +832,7 @@
         <v>30</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>8</v>
@@ -846,22 +843,22 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="2"/>
-      <c r="C16" s="2">
+      <c r="C16" s="3">
         <v>18</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="2" t="s">
+      <c r="F16" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="3"/>
       <c r="I16" s="2"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.25">
@@ -873,7 +870,7 @@
         <v>33</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>11</v>
@@ -882,7 +879,7 @@
         <v>14</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I17" s="2"/>
     </row>
@@ -895,7 +892,7 @@
         <v>34</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>11</v>
@@ -904,7 +901,7 @@
         <v>14</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I18" s="2"/>
     </row>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -925,20 +925,20 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B20" s="2"/>
-      <c r="C20" s="2">
+      <c r="C20" s="3">
         <v>21</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2" t="s">
-        <v>41</v>
-      </c>
+      <c r="F20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="3"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="2"/>
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
@@ -339,7 +339,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -374,7 +374,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -727,20 +727,20 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="2"/>
-      <c r="C10" s="2">
+      <c r="C10" s="3">
         <v>13</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3"/>
+      <c r="H10" s="3"/>
       <c r="I10" s="2"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>s/n</t>
   </si>
@@ -191,6 +191,9 @@
   </si>
   <si>
     <t>details required (Copy pending)</t>
+  </si>
+  <si>
+    <t>print</t>
   </si>
 </sst>
 </file>
@@ -943,20 +946,22 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="2"/>
-      <c r="C21" s="2">
+      <c r="C21" s="3">
         <v>22</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
+      <c r="F21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G21" s="3"/>
+      <c r="H21" s="3" t="s">
+        <v>59</v>
+      </c>
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="71">
   <si>
     <t>s/n</t>
   </si>
@@ -194,6 +194,42 @@
   </si>
   <si>
     <t>print</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Front end </t>
+  </si>
+  <si>
+    <t>incomplete</t>
+  </si>
+  <si>
+    <t>order return/cancel</t>
+  </si>
+  <si>
+    <t>country dropdown</t>
+  </si>
+  <si>
+    <t>Front end checkout page</t>
+  </si>
+  <si>
+    <t>payment</t>
+  </si>
+  <si>
+    <t>full payment,delivery charge only,promocode,show total</t>
+  </si>
+  <si>
+    <t>product details</t>
+  </si>
+  <si>
+    <t># When select/click picture for details – under the picture 1. Products details 2.Color and Sizes 3.
+Description and 4. Delivery Guarantee (Delivery Time and Delivery charge # Dhaka Metro 1-3 working
+days, charge 60tk # Dhaka suburb area 2-5 working days, charge 100tk # Bangladesh wide 2-5 working days,
+120tk.)</t>
+  </si>
+  <si>
+    <t>login bonus</t>
+  </si>
+  <si>
+    <t>daily customer login bonus,social login</t>
   </si>
 </sst>
 </file>
@@ -264,7 +300,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -280,6 +316,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -586,7 +625,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I27"/>
+  <dimension ref="B3:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1040,23 +1079,121 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="C26" s="2">
+        <v>25</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
+      <c r="G26" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="I26" s="2"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="C27" s="2">
+        <v>27</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="G27" s="2" t="s">
+        <v>61</v>
+      </c>
       <c r="H27" s="2"/>
       <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2">
+        <v>28</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2">
+        <v>29</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I29" s="2"/>
+    </row>
+    <row r="30" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2">
+        <v>31</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2">
+        <v>32</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="72">
   <si>
     <t>s/n</t>
   </si>
@@ -230,6 +230,9 @@
   </si>
   <si>
     <t>daily customer login bonus,social login</t>
+  </si>
+  <si>
+    <t>complete</t>
   </si>
 </sst>
 </file>
@@ -317,7 +320,7 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1079,23 +1082,23 @@
     </row>
     <row r="26" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B26" s="2"/>
-      <c r="C26" s="2">
+      <c r="C26" s="3">
         <v>25</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I26" s="2"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I26" s="3"/>
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
@@ -1157,23 +1160,23 @@
     </row>
     <row r="30" spans="2:9" ht="120" x14ac:dyDescent="0.25">
       <c r="B30" s="2"/>
-      <c r="C30" s="2">
+      <c r="C30" s="3">
         <v>31</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="3" t="s">
         <v>67</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I30" s="2"/>
+      <c r="F30" s="3"/>
+      <c r="G30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I30" s="3"/>
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="2"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
   <si>
     <t>s/n</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>complete</t>
+  </si>
+  <si>
+    <t>Order Confirmation</t>
+  </si>
+  <si>
+    <t>after order a mail send</t>
   </si>
 </sst>
 </file>
@@ -628,7 +634,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I31"/>
+  <dimension ref="B3:I33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1102,41 +1108,41 @@
     </row>
     <row r="27" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B27" s="2"/>
-      <c r="C27" s="2">
+      <c r="C27" s="3">
         <v>27</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B28" s="2"/>
-      <c r="C28" s="2">
+      <c r="C28" s="3">
         <v>28</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
+      <c r="F28" s="3"/>
+      <c r="G28" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H28" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H28" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28" s="2"/>
+      <c r="I28" s="3"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
@@ -1198,6 +1204,29 @@
       </c>
       <c r="I31" s="2"/>
     </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3">
+        <v>33</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I32" s="3"/>
+    </row>
+    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
+      <c r="D33"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
   <si>
     <t>s/n</t>
   </si>
@@ -239,6 +239,12 @@
   </si>
   <si>
     <t>after order a mail send</t>
+  </si>
+  <si>
+    <t>reject item</t>
+  </si>
+  <si>
+    <t>under report reject item,cancell item confusion</t>
   </si>
 </sst>
 </file>
@@ -309,7 +315,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -329,6 +335,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Good" xfId="1" builtinId="26"/>
@@ -1013,24 +1020,24 @@
       <c r="I21" s="2"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3">
         <v>23</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F22" s="2" t="s">
+      <c r="F22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2" t="s">
+      <c r="G22" s="3"/>
+      <c r="H22" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="I22" s="2"/>
+      <c r="I22" s="3"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B23" s="2"/>
@@ -1224,8 +1231,25 @@
       </c>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33"/>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B33" s="7"/>
+      <c r="C33" s="7">
+        <v>34</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="I33" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
   <si>
     <t>s/n</t>
   </si>
@@ -245,6 +245,12 @@
   </si>
   <si>
     <t>under report reject item,cancell item confusion</t>
+  </si>
+  <si>
+    <t>gross profit summary</t>
+  </si>
+  <si>
+    <t>confution</t>
   </si>
 </sst>
 </file>
@@ -641,7 +647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I33"/>
+  <dimension ref="B3:I34"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1251,6 +1257,26 @@
       </c>
       <c r="I33" s="7"/>
     </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3">
+        <v>34</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="3"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
   <si>
     <t>s/n</t>
   </si>
@@ -251,13 +251,25 @@
   </si>
   <si>
     <t>confution</t>
+  </si>
+  <si>
+    <t>sales status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  confution</t>
+  </si>
+  <si>
+    <t>send parcel</t>
+  </si>
+  <si>
+    <t>change delivery status to dispatch,search order id,insert delivery company name,print delivery invoice</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +291,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -290,6 +309,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
   </fills>
@@ -317,11 +341,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -342,8 +367,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="2" builtinId="27"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -647,7 +676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I34"/>
+  <dimension ref="B3:I36"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1258,24 +1287,64 @@
       <c r="I33" s="7"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="3"/>
-      <c r="C34" s="3">
+      <c r="B34" s="8"/>
+      <c r="C34" s="8">
         <v>34</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="D34" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="E34" s="3" t="s">
+      <c r="E34" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3" t="s">
+      <c r="F34" s="8"/>
+      <c r="G34" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="H34" s="3" t="s">
+      <c r="H34" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="3"/>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B35" s="8"/>
+      <c r="C35" s="8">
+        <v>35</v>
+      </c>
+      <c r="D35" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H35" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B36" s="2"/>
+      <c r="C36" s="3">
+        <v>36</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="118">
   <si>
     <t>s/n</t>
   </si>
@@ -262,7 +262,149 @@
     <t>send parcel</t>
   </si>
   <si>
-    <t>change delivery status to dispatch,search order id,insert delivery company name,print delivery invoice</t>
+    <t>image not showing, color and size confution</t>
+  </si>
+  <si>
+    <t>image not showing</t>
+  </si>
+  <si>
+    <t>best customer</t>
+  </si>
+  <si>
+    <t>sms api required,send email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer </t>
+  </si>
+  <si>
+    <t>customer search,receive invoice with image,when delivery status change to dispatch then receive email,when any change of status customer receive email</t>
+  </si>
+  <si>
+    <t xml:space="preserve">data insert </t>
+  </si>
+  <si>
+    <t>country,district,thana,postcode with all delivery charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">product sku </t>
+  </si>
+  <si>
+    <t>unique data validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Different colour product  </t>
+  </si>
+  <si>
+    <t>but same design can be added together with different
+SKU/code number. Such as same design but different colour when customer change
+colour sku number will change. Confusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin Power- </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Option to provide limited power to staff.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">customer support </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text and Email – </t>
+  </si>
+  <si>
+    <t xml:space="preserve">option to send bulk text and email to customer for special
+promotion or any information.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Notification </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> customer can message us and at the same time or later we can reply
+to customer, its kind of live chat but not 100%.
+</t>
+  </si>
+  <si>
+    <t>Promo code/coupon –</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  option for promotional offer where we can generate promo
+code and automatic generate which was advised by Innovative Technology &amp;
+Engineering
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">change delivery status to dispatch,search order id,insert delivery company name,print delivery invoice like Delivery Invoice Format
+</t>
+  </si>
+  <si>
+    <t>backup</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  . Data – Option to save all the data in my computer or external hard drive. 
+</t>
+  </si>
+  <si>
+    <t>Email Greeting -</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Hi Riaz, Thanking you to shop with BiGshot. Your order has successfully
+placed. You will receive your parcel within # Dhaka Metro 1-3 working days # Bangladesh
+wide 2-5 working days. You can find out the update or cancel/return your order in your
+account under “order history”. Your order details following. (following should be customer
+invoice).
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Dispatch Email: Hi Riaz, we are pleased to let you know your parcel is on the way.
+You will receive your parcel within # Dhaka Metro 1-3 working days # Bangladesh wide 2-
+5 working days. We guarantee 100% satisfaction, if you are not happy with our products or
+received a faulty or wrong item, you can return within 7 days since you received parcel. You
+can easily return/cancel from your account under “Order History”. Please find out our
+Return policy. (active link)
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dispatch Email: </t>
+  </si>
+  <si>
+    <t xml:space="preserve">. Delivered Email </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hi Riaz, your parcel already delivered, if you didn’t receive please
+contact us immediate. We guarantee 100% satisfaction, if you are not happy with our
+products or received a faulty or wrong item, you can return within 7 days since you received
+parcel. You can easily return/cancel from your account under “Order History”. Please find
+out our Return policy. (blue colour text active link)
+</t>
+  </si>
+  <si>
+    <t>Discount/sale –</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> need option to put stock on sale/discount. It will appear before
+existing price ( tk750 tk1,000) which means now 750 and was 1000, use icon of bd tk. Find
+out www.nastygal.com go in the sales item.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Delivery charge </t>
+  </si>
+  <si>
+    <t xml:space="preserve">need option to offer free delivery charge such as if customer
+buy more than 5,000 tk no delivery charge which will be automatic deduct when we
+put this offer on.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">quick report </t>
+  </si>
+  <si>
+    <t xml:space="preserve">incomplete
+</t>
+  </si>
+  <si>
+    <t>sku download</t>
   </si>
 </sst>
 </file>
@@ -346,7 +488,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -369,6 +511,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -676,7 +821,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I36"/>
+  <dimension ref="B3:I56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1289,7 +1434,7 @@
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
       <c r="C34" s="8">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D34" s="8" t="s">
         <v>76</v>
@@ -1326,25 +1471,425 @@
       </c>
       <c r="I35" s="8"/>
     </row>
-    <row r="36" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B36" s="2"/>
-      <c r="C36" s="3">
+    <row r="36" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B36" s="8"/>
+      <c r="C36" s="8">
         <v>36</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="F36" s="8"/>
+      <c r="G36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H36" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="8"/>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B37" s="8"/>
+      <c r="C37" s="8">
+        <v>37</v>
+      </c>
+      <c r="D37" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="I36" s="3"/>
+      <c r="F37" s="8"/>
+      <c r="G37" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H37" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B38" s="8"/>
+      <c r="C38" s="8">
+        <v>38</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="9" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="8"/>
+      <c r="G38" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H38" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I38" s="8"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B39" s="8"/>
+      <c r="C39" s="8">
+        <v>39</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H39" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I39" s="8"/>
+    </row>
+    <row r="40" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8">
+        <v>40</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="E40" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="F40" s="8"/>
+      <c r="G40" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H40" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="2:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="B41" s="8"/>
+      <c r="C41" s="8">
+        <v>41</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="E41" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F41" s="8"/>
+      <c r="G41" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H41" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" s="8"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="8"/>
+      <c r="C42" s="8">
+        <v>42</v>
+      </c>
+      <c r="D42" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="E42" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="F42" s="8"/>
+      <c r="G42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H42" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B43" s="8"/>
+      <c r="C43" s="8">
+        <v>43</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="F43" s="8"/>
+      <c r="G43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I43" s="8"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B44" s="8"/>
+      <c r="C44" s="8">
+        <v>44</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E44" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="8"/>
+      <c r="G44" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="8"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B45" s="8"/>
+      <c r="C45" s="8">
+        <v>45</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" s="8"/>
+      <c r="G45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="B46" s="8"/>
+      <c r="C46" s="8">
+        <v>46</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H46" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I46" s="8"/>
+    </row>
+    <row r="47" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="B47" s="8"/>
+      <c r="C47" s="8">
+        <v>47</v>
+      </c>
+      <c r="D47" s="8" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="F47" s="8"/>
+      <c r="G47" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H47" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I47" s="8"/>
+    </row>
+    <row r="48" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="B48" s="8"/>
+      <c r="C48" s="8">
+        <v>48</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="9" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="8"/>
+      <c r="G48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H48" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" s="8"/>
+    </row>
+    <row r="49" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B49" s="8"/>
+      <c r="C49" s="8">
+        <v>48</v>
+      </c>
+      <c r="D49" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="E49" s="9" t="s">
+        <v>104</v>
+      </c>
+      <c r="F49" s="8"/>
+      <c r="G49" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H49" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I49" s="8"/>
+    </row>
+    <row r="50" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="B50" s="8"/>
+      <c r="C50" s="8">
+        <v>48</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="E50" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I50" s="8"/>
+    </row>
+    <row r="51" spans="2:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="B51" s="8"/>
+      <c r="C51" s="8">
+        <v>48</v>
+      </c>
+      <c r="D51" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="E51" s="9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H51" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I51" s="8"/>
+    </row>
+    <row r="52" spans="2:9" ht="180" x14ac:dyDescent="0.25">
+      <c r="B52" s="8"/>
+      <c r="C52" s="8">
+        <v>48</v>
+      </c>
+      <c r="D52" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="E52" s="9" t="s">
+        <v>110</v>
+      </c>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H52" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I52" s="8"/>
+    </row>
+    <row r="53" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="B53" s="8"/>
+      <c r="C53" s="8">
+        <v>48</v>
+      </c>
+      <c r="D53" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="E53" s="9" t="s">
+        <v>112</v>
+      </c>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H53" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I53" s="8"/>
+    </row>
+    <row r="54" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="B54" s="8"/>
+      <c r="C54" s="8">
+        <v>48</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E54" s="9" t="s">
+        <v>114</v>
+      </c>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H54" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I54" s="8"/>
+    </row>
+    <row r="55" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B55" s="8"/>
+      <c r="C55" s="8">
+        <v>48</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="E55" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H55" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I55" s="8"/>
+    </row>
+    <row r="56" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+      <c r="B56" s="8"/>
+      <c r="C56" s="8">
+        <v>48</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="E56" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H56" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="I56" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -250,13 +250,7 @@
     <t>gross profit summary</t>
   </si>
   <si>
-    <t>confution</t>
-  </si>
-  <si>
     <t>sales status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  confution</t>
   </si>
   <si>
     <t>send parcel</t>
@@ -405,6 +399,12 @@
   </si>
   <si>
     <t>sku download</t>
+  </si>
+  <si>
+    <t>confusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  confusion</t>
   </si>
 </sst>
 </file>
@@ -1440,7 +1440,7 @@
         <v>76</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>77</v>
+        <v>116</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8" t="s">
@@ -1452,24 +1452,24 @@
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="8"/>
-      <c r="C35" s="8">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3">
         <v>35</v>
       </c>
-      <c r="D35" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="E35" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H35" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I35" s="8"/>
+      <c r="D35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
@@ -1477,10 +1477,10 @@
         <v>36</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F36" s="8"/>
       <c r="G36" s="8" t="s">
@@ -1492,24 +1492,24 @@
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B37" s="8"/>
-      <c r="C37" s="8">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3">
         <v>37</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="E37" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I37" s="8"/>
+      <c r="E37" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I37" s="3"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
@@ -1520,7 +1520,7 @@
         <v>39</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F38" s="8"/>
       <c r="G38" s="8" t="s">
@@ -1537,10 +1537,10 @@
         <v>39</v>
       </c>
       <c r="D39" s="8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F39" s="8"/>
       <c r="G39" s="8" t="s">
@@ -1557,10 +1557,10 @@
         <v>40</v>
       </c>
       <c r="D40" s="8" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F40" s="8"/>
       <c r="G40" s="8" t="s">
@@ -1577,10 +1577,10 @@
         <v>41</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F41" s="8"/>
       <c r="G41" s="8" t="s">
@@ -1597,10 +1597,10 @@
         <v>42</v>
       </c>
       <c r="D42" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E42" s="9" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F42" s="8"/>
       <c r="G42" s="8" t="s">
@@ -1617,10 +1617,10 @@
         <v>43</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F43" s="8"/>
       <c r="G43" s="8" t="s">
@@ -1637,10 +1637,10 @@
         <v>44</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E44" s="9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F44" s="8"/>
       <c r="G44" s="8" t="s">
@@ -1657,7 +1657,7 @@
         <v>45</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>61</v>
@@ -1677,10 +1677,10 @@
         <v>46</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F46" s="8"/>
       <c r="G46" s="8" t="s">
@@ -1697,10 +1697,10 @@
         <v>47</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F47" s="8"/>
       <c r="G47" s="8" t="s">
@@ -1717,10 +1717,10 @@
         <v>48</v>
       </c>
       <c r="D48" s="8" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E48" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F48" s="8"/>
       <c r="G48" s="8" t="s">
@@ -1737,10 +1737,10 @@
         <v>48</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
@@ -1757,10 +1757,10 @@
         <v>48</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E50" s="9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F50" s="8"/>
       <c r="G50" s="8" t="s">
@@ -1777,10 +1777,10 @@
         <v>48</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F51" s="8"/>
       <c r="G51" s="8" t="s">
@@ -1797,10 +1797,10 @@
         <v>48</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E52" s="9" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F52" s="8"/>
       <c r="G52" s="8" t="s">
@@ -1817,10 +1817,10 @@
         <v>48</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="F53" s="8"/>
       <c r="G53" s="8" t="s">
@@ -1837,10 +1837,10 @@
         <v>48</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E54" s="9" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F54" s="8"/>
       <c r="G54" s="8" t="s">
@@ -1857,10 +1857,10 @@
         <v>48</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="s">
@@ -1877,10 +1877,10 @@
         <v>48</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E56" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F56" s="8"/>
       <c r="G56" s="8" t="s">

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
   <si>
     <t>s/n</t>
   </si>
@@ -405,6 +405,10 @@
   </si>
   <si>
     <t xml:space="preserve">  confusion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">complete
+</t>
   </si>
 </sst>
 </file>
@@ -1472,24 +1476,24 @@
       <c r="I35" s="3"/>
     </row>
     <row r="36" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B36" s="8"/>
-      <c r="C36" s="8">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3">
         <v>36</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="E36" s="9" t="s">
+      <c r="E36" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H36" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I36" s="8"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I36" s="3"/>
     </row>
     <row r="37" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B37" s="3"/>
@@ -1512,44 +1516,44 @@
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B38" s="8"/>
-      <c r="C38" s="8">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3">
         <v>38</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="9" t="s">
+      <c r="E38" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="F38" s="8"/>
-      <c r="G38" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H38" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I38" s="8"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
-      <c r="C39" s="8">
+      <c r="C39" s="3">
         <v>39</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E39" s="9" t="s">
+      <c r="E39" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F39" s="8"/>
-      <c r="G39" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H39" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I39" s="8"/>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I39" s="3"/>
     </row>
     <row r="40" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B40" s="8"/>
@@ -1752,24 +1756,24 @@
       <c r="I49" s="8"/>
     </row>
     <row r="50" spans="2:9" ht="150" x14ac:dyDescent="0.25">
-      <c r="B50" s="8"/>
-      <c r="C50" s="8">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3">
         <v>48</v>
       </c>
-      <c r="D50" s="8" t="s">
+      <c r="D50" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="9" t="s">
+      <c r="E50" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H50" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I50" s="8"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="3"/>
     </row>
     <row r="51" spans="2:9" ht="195" x14ac:dyDescent="0.25">
       <c r="B51" s="8"/>
@@ -1872,24 +1876,24 @@
       <c r="I55" s="8"/>
     </row>
     <row r="56" spans="2:9" ht="45" x14ac:dyDescent="0.25">
-      <c r="B56" s="8"/>
-      <c r="C56" s="8">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3">
         <v>48</v>
       </c>
-      <c r="D56" s="9" t="s">
+      <c r="D56" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="E56" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H56" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I56" s="8"/>
+      <c r="E56" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I56" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -889,21 +889,21 @@
     </row>
     <row r="6" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B6" s="2"/>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>10</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="2"/>
@@ -1556,24 +1556,24 @@
       <c r="I39" s="3"/>
     </row>
     <row r="40" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B40" s="8"/>
-      <c r="C40" s="8">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3">
         <v>40</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E40" s="9" t="s">
+      <c r="E40" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="F40" s="8"/>
-      <c r="G40" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H40" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I40" s="8"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I40" s="3"/>
     </row>
     <row r="41" spans="2:9" ht="30" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
@@ -1617,23 +1617,23 @@
     </row>
     <row r="43" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
-      <c r="C43" s="8">
+      <c r="C43" s="3">
         <v>43</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E43" s="9" t="s">
+      <c r="E43" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="F43" s="8"/>
-      <c r="G43" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H43" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I43" s="8"/>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I43" s="3"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B44" s="8"/>
@@ -1816,24 +1816,24 @@
       <c r="I52" s="8"/>
     </row>
     <row r="53" spans="2:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="B53" s="8"/>
-      <c r="C53" s="8">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3">
         <v>48</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="E53" s="9" t="s">
+      <c r="E53" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="F53" s="8"/>
-      <c r="G53" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H53" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I53" s="8"/>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="I53" s="3"/>
     </row>
     <row r="54" spans="2:9" ht="105" x14ac:dyDescent="0.25">
       <c r="B54" s="8"/>

--- a/workStatus/workStatus.xlsx
+++ b/workStatus/workStatus.xlsx
@@ -10,11 +10,12 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="122211"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="110">
   <si>
     <t>s/n</t>
   </si>
@@ -209,12 +210,6 @@
   </si>
   <si>
     <t>Front end checkout page</t>
-  </si>
-  <si>
-    <t>payment</t>
-  </si>
-  <si>
-    <t>full payment,delivery charge only,promocode,show total</t>
   </si>
   <si>
     <t>product details</t>
@@ -298,34 +293,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Option to provide limited power to staff.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">customer support </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text and Email – </t>
-  </si>
-  <si>
-    <t xml:space="preserve">option to send bulk text and email to customer for special
-promotion or any information.
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notification </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> customer can message us and at the same time or later we can reply
-to customer, its kind of live chat but not 100%.
-</t>
-  </si>
-  <si>
-    <t>Promo code/coupon –</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  option for promotional offer where we can generate promo
-code and automatic generate which was advised by Innovative Technology &amp;
-Engineering
-</t>
   </si>
   <si>
     <t xml:space="preserve">change delivery status to dispatch,search order id,insert delivery company name,print delivery invoice like Delivery Invoice Format
@@ -382,15 +349,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Free Delivery charge </t>
-  </si>
-  <si>
-    <t xml:space="preserve">need option to offer free delivery charge such as if customer
-buy more than 5,000 tk no delivery charge which will be automatic deduct when we
-put this offer on.
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">quick report </t>
   </si>
   <si>
@@ -409,13 +367,20 @@
   <si>
     <t xml:space="preserve">complete
 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+</t>
+  </si>
+  <si>
+    <t>after complete the project</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,8 +409,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -462,8 +435,13 @@
         <fgColor rgb="FFFFC7CE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -486,13 +464,29 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -519,9 +513,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="3" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
+    <cellStyle name="Calculation" xfId="3" builtinId="22"/>
     <cellStyle name="Good" xfId="1" builtinId="26"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
@@ -530,9 +531,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -825,7 +823,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B3:I56"/>
+  <dimension ref="B3:J59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="20.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1290,10 +1288,10 @@
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I26" s="3"/>
     </row>
@@ -1310,7 +1308,7 @@
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
@@ -1328,7 +1326,7 @@
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>61</v>
@@ -1337,22 +1335,12 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="2"/>
-      <c r="C29" s="2">
-        <v>29</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>61</v>
-      </c>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
       <c r="I29" s="2"/>
     </row>
     <row r="30" spans="2:9" ht="120" x14ac:dyDescent="0.25">
@@ -1361,17 +1349,17 @@
         <v>31</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I30" s="3"/>
     </row>
@@ -1381,10 +1369,10 @@
         <v>32</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F31" s="2"/>
       <c r="G31" s="2" t="s">
@@ -1401,17 +1389,17 @@
         <v>33</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I32" s="3"/>
     </row>
@@ -1421,17 +1409,17 @@
         <v>34</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H33" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I33" s="7"/>
     </row>
@@ -1441,10 +1429,10 @@
         <v>24</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E34" s="8" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="F34" s="8"/>
       <c r="G34" s="8" t="s">
@@ -1461,17 +1449,17 @@
         <v>35</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I35" s="3"/>
     </row>
@@ -1481,17 +1469,17 @@
         <v>36</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I36" s="3"/>
     </row>
@@ -1504,14 +1492,14 @@
         <v>37</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I37" s="3"/>
     </row>
@@ -1524,34 +1512,34 @@
         <v>39</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I38" s="3"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B39" s="8"/>
+      <c r="B39" s="10"/>
       <c r="C39" s="3">
         <v>39</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I39" s="3"/>
     </row>
@@ -1561,59 +1549,59 @@
         <v>40</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I40" s="3"/>
     </row>
     <row r="41" spans="2:9" ht="30" x14ac:dyDescent="0.25">
-      <c r="B41" s="8"/>
-      <c r="C41" s="8">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3">
         <v>41</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F41" s="3"/>
+      <c r="G41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I41" s="3"/>
+    </row>
+    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3">
+        <v>42</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E42" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="F41" s="8"/>
-      <c r="G41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H41" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I41" s="8"/>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B42" s="8"/>
-      <c r="C42" s="8">
-        <v>42</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="E42" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="F42" s="8"/>
-      <c r="G42" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H42" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I42" s="8"/>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I42" s="3"/>
     </row>
     <row r="43" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
@@ -1621,130 +1609,60 @@
         <v>43</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I43" s="3"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B44" s="8"/>
-      <c r="C44" s="8">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3">
         <v>44</v>
       </c>
-      <c r="D44" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" s="9" t="s">
-        <v>92</v>
-      </c>
-      <c r="F44" s="8"/>
-      <c r="G44" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H44" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I44" s="8"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B45" s="8"/>
-      <c r="C45" s="8">
-        <v>45</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="E45" s="9" t="s">
-        <v>61</v>
-      </c>
-      <c r="F45" s="8"/>
-      <c r="G45" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I45" s="8"/>
-    </row>
-    <row r="46" spans="2:9" ht="60" x14ac:dyDescent="0.25">
-      <c r="B46" s="8"/>
-      <c r="C46" s="8">
-        <v>46</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="E46" s="9" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H46" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I46" s="8"/>
-    </row>
-    <row r="47" spans="2:9" ht="75" x14ac:dyDescent="0.25">
-      <c r="B47" s="8"/>
-      <c r="C47" s="8">
-        <v>47</v>
-      </c>
-      <c r="D47" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="E47" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H47" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I47" s="8"/>
-    </row>
-    <row r="48" spans="2:9" ht="90" x14ac:dyDescent="0.25">
+      <c r="D44" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I44" s="3"/>
+    </row>
+    <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="8"/>
-      <c r="C48" s="8">
-        <v>48</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="E48" s="9" t="s">
-        <v>99</v>
-      </c>
+      <c r="C48" s="8"/>
+      <c r="D48" s="8"/>
+      <c r="E48" s="9"/>
       <c r="F48" s="8"/>
-      <c r="G48" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H48" s="8" t="s">
-        <v>61</v>
-      </c>
+      <c r="G48" s="8"/>
+      <c r="H48" s="8"/>
       <c r="I48" s="8"/>
     </row>
-    <row r="49" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B49" s="8"/>
       <c r="C49" s="8">
         <v>48</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="F49" s="8"/>
       <c r="G49" s="8" t="s">
@@ -1755,116 +1673,108 @@
       </c>
       <c r="I49" s="8"/>
     </row>
-    <row r="50" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" ht="150" x14ac:dyDescent="0.25">
       <c r="B50" s="3"/>
       <c r="C50" s="3">
         <v>48</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I50" s="3"/>
     </row>
-    <row r="51" spans="2:9" ht="195" x14ac:dyDescent="0.25">
-      <c r="B51" s="8"/>
-      <c r="C51" s="8">
+    <row r="51" spans="2:10" ht="195" x14ac:dyDescent="0.25">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3">
         <v>48</v>
       </c>
-      <c r="D51" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H51" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I51" s="8"/>
-    </row>
-    <row r="52" spans="2:9" ht="180" x14ac:dyDescent="0.25">
-      <c r="B52" s="8"/>
-      <c r="C52" s="8">
+      <c r="D51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F51" s="3"/>
+      <c r="G51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I51" s="3"/>
+    </row>
+    <row r="52" spans="2:10" ht="180" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3">
         <v>48</v>
       </c>
-      <c r="D52" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="9" t="s">
-        <v>108</v>
-      </c>
-      <c r="F52" s="8"/>
-      <c r="G52" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H52" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I52" s="8"/>
-    </row>
-    <row r="53" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="D52" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F52" s="3"/>
+      <c r="G52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="I52" s="3"/>
+    </row>
+    <row r="53" spans="2:10" ht="120" x14ac:dyDescent="0.25">
       <c r="B53" s="3"/>
       <c r="C53" s="3">
         <v>48</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="F53" s="3"/>
       <c r="G53" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H53" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I53" s="3"/>
     </row>
-    <row r="54" spans="2:9" ht="105" x14ac:dyDescent="0.25">
-      <c r="B54" s="8"/>
-      <c r="C54" s="8">
-        <v>48</v>
-      </c>
-      <c r="D54" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E54" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F54" s="8"/>
-      <c r="G54" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="H54" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I54" s="8"/>
-    </row>
-    <row r="55" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="10"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F54" s="10"/>
+      <c r="G54" s="10"/>
+      <c r="H54" s="10"/>
+      <c r="I54" s="10"/>
+    </row>
+    <row r="55" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B55" s="8"/>
       <c r="C55" s="8">
         <v>48</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="F55" s="8"/>
       <c r="G55" s="8" t="s">
@@ -1875,25 +1785,55 @@
       </c>
       <c r="I55" s="8"/>
     </row>
-    <row r="56" spans="2:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:10" ht="45" x14ac:dyDescent="0.25">
       <c r="B56" s="3"/>
       <c r="C56" s="3">
         <v>48</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F56" s="3"/>
       <c r="G56" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="11"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C58" s="10"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="10"/>
+      <c r="H58" s="10"/>
+      <c r="I58" s="10"/>
+      <c r="J58" s="10"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C59" s="10"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10"/>
+      <c r="F59" s="11"/>
+      <c r="G59" s="10"/>
+      <c r="H59" s="10"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
